--- a/data/trans_orig/P05B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05B_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>22043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37762</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472758</t>
+          <t>472021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487569</t>
+          <t>487052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>445431</t>
+          <t>445303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>459085</t>
+          <t>459281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>923791</t>
+          <t>922622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>943700</t>
+          <t>943849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41392</t>
+          <t>41749</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67582</t>
+          <t>67478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701612</t>
+          <t>699986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>722064</t>
+          <t>720809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>582478</t>
+          <t>582121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604371</t>
+          <t>604193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1291776</t>
+          <t>1291880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1320761</t>
+          <t>1322208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28835</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53745</t>
+          <t>54529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47899</t>
+          <t>49211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80964</t>
+          <t>79568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602957</t>
+          <t>602578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624401</t>
+          <t>623989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635999</t>
+          <t>635215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660909</t>
+          <t>660607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1247448</t>
+          <t>1248844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1280513</t>
+          <t>1279201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31413</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20720</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>500573</t>
+          <t>500448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514118</t>
+          <t>514147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484229</t>
+          <t>484150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>501821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>990965</t>
+          <t>989919</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014069</t>
+          <t>1013608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24439</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30676</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46980</t>
+          <t>46948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361372</t>
+          <t>362088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377391</t>
+          <t>377294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373310</t>
+          <t>373970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391802</t>
+          <t>391826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>742817</t>
+          <t>742849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766015</t>
+          <t>767108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>30316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284885</t>
+          <t>284061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291770</t>
+          <t>291746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313813</t>
+          <t>312618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329313</t>
+          <t>330035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>601345</t>
+          <t>603115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>619179</t>
+          <t>619857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190444</t>
+          <t>190129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201692</t>
+          <t>201604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310604</t>
+          <t>311587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326854</t>
+          <t>327000</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>506467</t>
+          <t>506033</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>526270</t>
+          <t>524914</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118038</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>135032</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183332</t>
+          <t>183299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224001</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>289091</t>
+          <t>289010</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3154386</t>
+          <t>3153265</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3194603</t>
+          <t>3193198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3194241</t>
+          <t>3194274</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3241790</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6360906</t>
+          <t>6360987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6425996</t>
+          <t>6424960</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442363</t>
+          <t>442530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451292</t>
+          <t>451303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415760</t>
+          <t>415567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427121</t>
+          <t>427148</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863370</t>
+          <t>863029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>876657</t>
+          <t>877339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21206</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35666</t>
+          <t>34221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661856</t>
+          <t>660485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676449</t>
+          <t>676417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>590752</t>
+          <t>589802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>603389</t>
+          <t>603333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1256683</t>
+          <t>1258128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1276837</t>
+          <t>1276781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657017</t>
+          <t>657236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673626</t>
+          <t>673555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684506</t>
+          <t>685283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701442</t>
+          <t>700774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1347434</t>
+          <t>1348847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1371283</t>
+          <t>1371865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16698</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589159</t>
+          <t>588051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>605863</t>
+          <t>605980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598478</t>
+          <t>598062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612027</t>
+          <t>611961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1192815</t>
+          <t>1193462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214120</t>
+          <t>1214493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12673</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>416796</t>
+          <t>416808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426384</t>
+          <t>426367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>430048</t>
+          <t>429972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439780</t>
+          <t>440585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851105</t>
+          <t>850684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864932</t>
+          <t>865147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298872</t>
+          <t>298837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343325</t>
+          <t>343382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648485</t>
+          <t>646273</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>657856</t>
+          <t>657849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16450</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238101</t>
+          <t>238457</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246776</t>
+          <t>246762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365921</t>
+          <t>365638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378118</t>
+          <t>378060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608567</t>
+          <t>608209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623698</t>
+          <t>623569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73995</t>
+          <t>72273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42825</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73961</t>
+          <t>74619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93701</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137168</t>
+          <t>141390</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3338807</t>
+          <t>3340529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3369810</t>
+          <t>3370708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3467626</t>
+          <t>3466968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3498762</t>
+          <t>3498440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6817221</t>
+          <t>6812999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6860688</t>
+          <t>6860196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>23218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410944</t>
+          <t>410455</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418414</t>
+          <t>418421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>372793</t>
+          <t>372559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387066</t>
+          <t>387917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>788229</t>
+          <t>789156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>804091</t>
+          <t>805255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>572506</t>
+          <t>572700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>584609</t>
+          <t>584606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>541826</t>
+          <t>541709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555396</t>
+          <t>555727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1119989</t>
+          <t>1120257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1138000</t>
+          <t>1137480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652591</t>
+          <t>654380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665012</t>
+          <t>665031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638274</t>
+          <t>639401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653154</t>
+          <t>653525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1297472</t>
+          <t>1297297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1315486</t>
+          <t>1316077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>20742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>621929</t>
+          <t>622402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638618</t>
+          <t>638605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>628214</t>
+          <t>628335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642551</t>
+          <t>643273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1257036</t>
+          <t>1255298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1279262</t>
+          <t>1278719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -8063,82 +8063,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>13048</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6882</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14120</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>12798</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6882</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2389</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14744</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>12798</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461686</t>
+          <t>461436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472377</t>
+          <t>472387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478703</t>
+          <t>479327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>491058</t>
+          <t>491080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>945790</t>
+          <t>944526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>961216</t>
+          <t>961150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323189</t>
+          <t>322111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333280</t>
+          <t>333275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>361025</t>
+          <t>361292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372693</t>
+          <t>372755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689375</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704128</t>
+          <t>704454</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23561</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>29178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245995</t>
+          <t>245549</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254579</t>
+          <t>254552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372676</t>
+          <t>372588</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>390068</t>
+          <t>390250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>623091</t>
+          <t>624057</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>642780</t>
+          <t>642784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62825</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97187</t>
+          <t>94563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>100422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>147346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3322810</t>
+          <t>3324342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3352148</t>
+          <t>3352559</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3433326</t>
+          <t>3435950</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3471021</t>
+          <t>3471677</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6771071</t>
+          <t>6768802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6815926</t>
+          <t>6815726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398026</t>
+          <t>404503</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>387545</t>
+          <t>397314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>307345</t>
+          <t>356847</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298361</t>
+          <t>348900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311591</t>
+          <t>361256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>705372</t>
+          <t>761350</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696022</t>
+          <t>753011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710474</t>
+          <t>766038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399822</t>
+          <t>406140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768652</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713022</t>
+          <t>768652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14741</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>15999</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>413856</t>
+          <t>467426</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403994</t>
+          <t>455726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420437</t>
+          <t>473129</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>505463</t>
+          <t>495198</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497352</t>
+          <t>488045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509757</t>
+          <t>499189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>919319</t>
+          <t>962624</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907404</t>
+          <t>949883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926791</t>
+          <t>969953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>529382</t>
+          <t>612662</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521732</t>
+          <t>604026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532913</t>
+          <t>616465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>586541</t>
+          <t>617600</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>581201</t>
+          <t>611606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>589464</t>
+          <t>620760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1115923</t>
+          <t>1230261</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1107356</t>
+          <t>1220713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1120847</t>
+          <t>1235464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>591272</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1126426</t>
+          <t>1241019</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1126426</t>
+          <t>1241019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1126426</t>
+          <t>1241019</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,22 +10729,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>882280</t>
+          <t>695061</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874910</t>
+          <t>689070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885373</t>
+          <t>698063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,27 +10842,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>704097</t>
+          <t>727370</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698666</t>
+          <t>721852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>707676</t>
+          <t>731535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1586378</t>
+          <t>1422431</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1579111</t>
+          <t>1415490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1592450</t>
+          <t>1427835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886330</t>
+          <t>699181</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886330</t>
+          <t>699181</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886330</t>
+          <t>699181</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711750</t>
+          <t>735754</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711750</t>
+          <t>735754</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711750</t>
+          <t>735754</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598081</t>
+          <t>1434935</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598081</t>
+          <t>1434935</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598081</t>
+          <t>1434935</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>551475</t>
+          <t>599685</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544425</t>
+          <t>592914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555768</t>
+          <t>604133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>537571</t>
+          <t>597214</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532394</t>
+          <t>591457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541429</t>
+          <t>601339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1089046</t>
+          <t>1196900</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1080931</t>
+          <t>1188516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1094881</t>
+          <t>1203258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559808</t>
+          <t>607959</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559808</t>
+          <t>607959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559808</t>
+          <t>607959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546159</t>
+          <t>606899</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546159</t>
+          <t>606899</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546159</t>
+          <t>606899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105967</t>
+          <t>1214859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105967</t>
+          <t>1214859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105967</t>
+          <t>1214859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,69 +11380,69 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6910</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11616</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6732</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>12258</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -11493,67 +11493,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>362377</t>
+          <t>400433</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>357753</t>
+          <t>395118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365100</t>
+          <t>403478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>429484</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>424778</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>432219</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>97,34%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>599515</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>593989</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>604241</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>961891</t>
+          <t>829917</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>955413</t>
+          <t>823496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968521</t>
+          <t>834598</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367533</t>
+          <t>406470</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367533</t>
+          <t>406470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367533</t>
+          <t>406470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606247</t>
+          <t>436394</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606247</t>
+          <t>436394</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606247</t>
+          <t>436394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973780</t>
+          <t>842864</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973780</t>
+          <t>842864</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973780</t>
+          <t>842864</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>279788</t>
+          <t>307078</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>275960</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>281573</t>
+          <t>308912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>418129</t>
+          <t>456390</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>414060</t>
+          <t>451887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>420676</t>
+          <t>459134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>697917</t>
+          <t>763468</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>693496</t>
+          <t>758185</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>701275</t>
+          <t>766742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423353</t>
+          <t>461968</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423353</t>
+          <t>461968</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423353</t>
+          <t>461968</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705508</t>
+          <t>771472</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705508</t>
+          <t>771472</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705508</t>
+          <t>771472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>68745</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>103457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3417184</t>
+          <t>3486850</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3398800</t>
+          <t>3470857</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3428620</t>
+          <t>3496648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3658661</t>
+          <t>3680101</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3645006</t>
+          <t>3667311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3670348</t>
+          <t>3690909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7075845</t>
+          <t>7166951</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7056554</t>
+          <t>7148967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7092998</t>
+          <t>7183679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
